--- a/Team-Data/2008-09/4-3-2008-09.xlsx
+++ b/Team-Data/2008-09/4-3-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E2" t="n">
         <v>43</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.573</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J2" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L2" t="n">
         <v>7.3</v>
@@ -691,40 +758,40 @@
         <v>20</v>
       </c>
       <c r="N2" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O2" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P2" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.736</v>
+        <v>0.735</v>
       </c>
       <c r="R2" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S2" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T2" t="n">
         <v>40.2</v>
       </c>
       <c r="U2" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V2" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W2" t="n">
         <v>7.4</v>
       </c>
       <c r="X2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z2" t="n">
         <v>19.5</v>
@@ -733,13 +800,13 @@
         <v>20.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -754,13 +821,13 @@
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ2" t="n">
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
@@ -772,10 +839,10 @@
         <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
@@ -784,25 +851,25 @@
         <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -858,13 +925,13 @@
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
         <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.487</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
         <v>6.5</v>
@@ -873,16 +940,16 @@
         <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
         <v>19.6</v>
       </c>
       <c r="P3" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.77</v>
+        <v>0.767</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
@@ -894,7 +961,7 @@
         <v>42.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.8</v>
@@ -903,25 +970,25 @@
         <v>7.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.1</v>
+        <v>100.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -960,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
         <v>21</v>
@@ -981,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -993,7 +1060,7 @@
         <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E4" t="n">
         <v>34</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>0.447</v>
+        <v>0.453</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J4" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
@@ -1055,22 +1122,22 @@
         <v>16.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O4" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P4" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="R4" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S4" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T4" t="n">
         <v>39.7</v>
@@ -1079,7 +1146,7 @@
         <v>21.4</v>
       </c>
       <c r="V4" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
@@ -1097,13 +1164,13 @@
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1115,7 +1182,7 @@
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>22</v>
@@ -1133,19 +1200,19 @@
         <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="n">
         <v>26</v>
       </c>
       <c r="AP4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
         <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS4" t="n">
         <v>23</v>
@@ -1178,7 +1245,7 @@
         <v>28</v>
       </c>
       <c r="BC4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -1207,55 +1274,55 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" t="n">
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.467</v>
+        <v>0.474</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
         <v>15.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O5" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="P5" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R5" t="n">
         <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
         <v>21</v>
@@ -1276,19 +1343,19 @@
         <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>101.9</v>
+        <v>102</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
@@ -1297,7 +1364,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
         <v>7</v>
@@ -1321,13 +1388,13 @@
         <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS5" t="n">
         <v>12</v>
@@ -1354,13 +1421,13 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
         <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -1407,28 +1474,28 @@
         <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
         <v>20.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.39</v>
+        <v>0.387</v>
       </c>
       <c r="O6" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.757</v>
+        <v>0.755</v>
       </c>
       <c r="R6" t="n">
         <v>10.7</v>
@@ -1437,37 +1504,37 @@
         <v>31.4</v>
       </c>
       <c r="T6" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U6" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V6" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W6" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X6" t="n">
         <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AB6" t="n">
         <v>100</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,13 +1549,13 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL6" t="n">
         <v>3</v>
@@ -1497,7 +1564,7 @@
         <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
@@ -1506,7 +1573,7 @@
         <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
         <v>20</v>
@@ -1521,22 +1588,22 @@
         <v>23</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
         <v>4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>0.592</v>
+        <v>0.6</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
@@ -1610,16 +1677,16 @@
         <v>22.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S7" t="n">
         <v>31.7</v>
       </c>
       <c r="T7" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U7" t="n">
         <v>21.5</v>
@@ -1628,7 +1695,7 @@
         <v>12.9</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X7" t="n">
         <v>5.3</v>
@@ -1637,7 +1704,7 @@
         <v>4.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA7" t="n">
         <v>20</v>
@@ -1646,10 +1713,10 @@
         <v>101.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI7" t="n">
         <v>8</v>
@@ -1670,7 +1737,7 @@
         <v>6</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL7" t="n">
         <v>12</v>
@@ -1691,7 +1758,7 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
         <v>6</v>
@@ -1706,7 +1773,7 @@
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1855,13 +1922,13 @@
         <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1873,13 +1940,13 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS8" t="n">
         <v>13</v>
       </c>
-      <c r="AS8" t="n">
-        <v>14</v>
-      </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU8" t="n">
         <v>5</v>
@@ -1888,7 +1955,7 @@
         <v>25</v>
       </c>
       <c r="AW8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX8" t="n">
         <v>2</v>
@@ -1903,7 +1970,7 @@
         <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
         <v>16</v>
@@ -2025,7 +2092,7 @@
         <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
@@ -2043,7 +2110,7 @@
         <v>29</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
         <v>29</v>
@@ -2055,13 +2122,13 @@
         <v>24</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU9" t="n">
         <v>16</v>
@@ -2076,7 +2143,7 @@
         <v>20</v>
       </c>
       <c r="AY9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
@@ -2088,7 +2155,7 @@
         <v>29</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
         <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>0.355</v>
+        <v>0.347</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="J10" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="K10" t="n">
         <v>0.46</v>
@@ -2144,19 +2211,19 @@
         <v>6.7</v>
       </c>
       <c r="M10" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="N10" t="n">
         <v>0.371</v>
       </c>
       <c r="O10" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="P10" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.79</v>
+        <v>0.789</v>
       </c>
       <c r="R10" t="n">
         <v>11.6</v>
@@ -2168,13 +2235,13 @@
         <v>42</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V10" t="n">
         <v>14.9</v>
       </c>
       <c r="W10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X10" t="n">
         <v>6.4</v>
@@ -2186,16 +2253,16 @@
         <v>22.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="AB10" t="n">
         <v>109.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.6</v>
+        <v>-3.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,16 +2274,16 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL10" t="n">
         <v>16</v>
@@ -2225,7 +2292,7 @@
         <v>17</v>
       </c>
       <c r="AN10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
         <v>1</v>
@@ -2240,10 +2307,10 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
         <v>14</v>
@@ -2267,7 +2334,7 @@
         <v>3</v>
       </c>
       <c r="BB10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E11" t="n">
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>0.632</v>
+        <v>0.64</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J11" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K11" t="n">
         <v>0.452</v>
@@ -2329,16 +2396,16 @@
         <v>20.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.375</v>
+        <v>0.377</v>
       </c>
       <c r="O11" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P11" t="n">
         <v>23.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="R11" t="n">
         <v>10.4</v>
@@ -2353,13 +2420,13 @@
         <v>20.4</v>
       </c>
       <c r="V11" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W11" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y11" t="n">
         <v>5.3</v>
@@ -2371,34 +2438,34 @@
         <v>20.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF11" t="n">
         <v>7</v>
       </c>
-      <c r="AF11" t="n">
-        <v>8</v>
-      </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
@@ -2407,10 +2474,10 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP11" t="n">
         <v>22</v>
@@ -2428,16 +2495,16 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY11" t="n">
         <v>23</v>
@@ -2446,13 +2513,13 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E12" t="n">
         <v>32</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>0.421</v>
+        <v>0.427</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J12" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L12" t="n">
         <v>7.9</v>
@@ -2511,16 +2578,16 @@
         <v>21</v>
       </c>
       <c r="N12" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O12" t="n">
         <v>18.3</v>
       </c>
       <c r="P12" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.804</v>
+        <v>0.805</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
@@ -2535,7 +2602,7 @@
         <v>21.7</v>
       </c>
       <c r="V12" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W12" t="n">
         <v>6.9</v>
@@ -2553,13 +2620,13 @@
         <v>20.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.2</v>
+        <v>104</v>
       </c>
       <c r="AC12" t="n">
         <v>-1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -2571,28 +2638,28 @@
         <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
         <v>4</v>
       </c>
       <c r="AM12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP12" t="n">
         <v>27</v>
@@ -2604,7 +2671,7 @@
         <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
         <v>2</v>
@@ -2613,7 +2680,7 @@
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW12" t="n">
         <v>23</v>
@@ -2628,10 +2695,10 @@
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
         <v>20</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,10 +2820,10 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>10</v>
@@ -2765,13 +2832,13 @@
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
         <v>28</v>
@@ -2786,7 +2853,7 @@
         <v>16</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>25</v>
@@ -2795,7 +2862,7 @@
         <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2804,10 +2871,10 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA13" t="n">
         <v>27</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -2863,22 +2930,22 @@
         <v>40.4</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="L14" t="n">
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="O14" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P14" t="n">
         <v>25.4</v>
@@ -2890,28 +2957,28 @@
         <v>12.5</v>
       </c>
       <c r="S14" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T14" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U14" t="n">
         <v>23.3</v>
       </c>
       <c r="V14" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA14" t="n">
         <v>22.1</v>
@@ -2920,10 +2987,10 @@
         <v>107.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2947,7 +3014,7 @@
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM14" t="n">
         <v>15</v>
@@ -2962,7 +3029,7 @@
         <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
@@ -2980,13 +3047,13 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ14" t="n">
         <v>12</v>
@@ -2998,7 +3065,7 @@
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
         <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
@@ -3048,16 +3115,16 @@
         <v>77.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
         <v>13.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.352</v>
+        <v>0.349</v>
       </c>
       <c r="O15" t="n">
         <v>19.2</v>
@@ -3066,7 +3133,7 @@
         <v>25.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R15" t="n">
         <v>10.5</v>
@@ -3075,16 +3142,16 @@
         <v>28.3</v>
       </c>
       <c r="T15" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="U15" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W15" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
         <v>4.6</v>
@@ -3099,34 +3166,34 @@
         <v>21.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.9</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF15" t="n">
         <v>26</v>
       </c>
-      <c r="AF15" t="n">
-        <v>25</v>
-      </c>
       <c r="AG15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI15" t="n">
         <v>30</v>
       </c>
       <c r="AJ15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3135,16 +3202,16 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
         <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
@@ -3162,7 +3229,7 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX15" t="n">
         <v>21</v>
@@ -3171,7 +3238,7 @@
         <v>26</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
@@ -3180,7 +3247,7 @@
         <v>30</v>
       </c>
       <c r="BC15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" t="n">
         <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>0.526</v>
+        <v>0.52</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
@@ -3227,7 +3294,7 @@
         <v>36.9</v>
       </c>
       <c r="J16" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K16" t="n">
         <v>0.455</v>
@@ -3236,28 +3303,28 @@
         <v>6.8</v>
       </c>
       <c r="M16" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O16" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P16" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.759</v>
+        <v>0.761</v>
       </c>
       <c r="R16" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S16" t="n">
         <v>29.1</v>
       </c>
       <c r="T16" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="U16" t="n">
         <v>20.4</v>
@@ -3266,7 +3333,7 @@
         <v>12.4</v>
       </c>
       <c r="W16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X16" t="n">
         <v>5.5</v>
@@ -3278,16 +3345,16 @@
         <v>20.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB16" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3305,7 +3372,7 @@
         <v>12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK16" t="n">
         <v>18</v>
@@ -3317,10 +3384,10 @@
         <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP16" t="n">
         <v>23</v>
@@ -3344,7 +3411,7 @@
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
         <v>5</v>
@@ -3359,7 +3426,7 @@
         <v>25</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" t="n">
         <v>32</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G17" t="n">
-        <v>0.421</v>
+        <v>0.416</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3412,22 +3479,22 @@
         <v>82.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L17" t="n">
         <v>6.1</v>
       </c>
       <c r="M17" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O17" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0.781</v>
@@ -3436,16 +3503,16 @@
         <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W17" t="n">
         <v>7.4</v>
@@ -3457,34 +3524,34 @@
         <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB17" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH17" t="n">
         <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
         <v>8</v>
@@ -3499,13 +3566,13 @@
         <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
         <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3514,7 +3581,7 @@
         <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
@@ -3523,7 +3590,7 @@
         <v>8</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
         <v>11</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F18" t="n">
         <v>54</v>
       </c>
       <c r="G18" t="n">
-        <v>0.289</v>
+        <v>0.28</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
@@ -3591,25 +3658,25 @@
         <v>36.4</v>
       </c>
       <c r="J18" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L18" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M18" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O18" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P18" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="Q18" t="n">
         <v>0.77</v>
@@ -3618,16 +3685,16 @@
         <v>11.9</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T18" t="n">
         <v>41.5</v>
       </c>
       <c r="U18" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V18" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W18" t="n">
         <v>6.2</v>
@@ -3648,25 +3715,25 @@
         <v>98.09999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-4.9</v>
+        <v>-5</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
       </c>
       <c r="AF18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ18" t="n">
         <v>7</v>
@@ -3675,37 +3742,37 @@
         <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
         <v>14</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
         <v>15</v>
       </c>
       <c r="AR18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS18" t="n">
         <v>19</v>
       </c>
       <c r="AT18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3717,13 +3784,13 @@
         <v>30</v>
       </c>
       <c r="AZ18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA18" t="n">
         <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
         <v>21</v>
       </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
         <v>21</v>
@@ -3860,7 +3927,7 @@
         <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN19" t="n">
         <v>11</v>
@@ -3878,7 +3945,7 @@
         <v>24</v>
       </c>
       <c r="AS19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
         <v>26</v>
@@ -3893,19 +3960,19 @@
         <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ19" t="n">
         <v>25</v>
       </c>
       <c r="BA19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E20" t="n">
         <v>47</v>
       </c>
       <c r="F20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20" t="n">
-        <v>0.627</v>
+        <v>0.635</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
       </c>
       <c r="I20" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J20" t="n">
-        <v>77.5</v>
+        <v>77.2</v>
       </c>
       <c r="K20" t="n">
         <v>0.457</v>
@@ -3964,10 +4031,10 @@
         <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O20" t="n">
         <v>18.5</v>
@@ -3976,16 +4043,16 @@
         <v>22.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S20" t="n">
         <v>30</v>
       </c>
       <c r="T20" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="U20" t="n">
         <v>19.8</v>
@@ -3997,34 +4064,34 @@
         <v>7.3</v>
       </c>
       <c r="X20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y20" t="n">
         <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AA20" t="n">
         <v>20.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG20" t="n">
         <v>8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>9</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -4033,10 +4100,10 @@
         <v>28</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL20" t="n">
         <v>11</v>
@@ -4048,10 +4115,10 @@
         <v>17</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
@@ -4069,19 +4136,19 @@
         <v>28</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA20" t="n">
         <v>16</v>
@@ -4090,7 +4157,7 @@
         <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4209,7 +4276,7 @@
         <v>23</v>
       </c>
       <c r="AH21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4230,16 +4297,16 @@
         <v>21</v>
       </c>
       <c r="AO21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP21" t="n">
         <v>20</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>19</v>
       </c>
       <c r="AQ21" t="n">
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS21" t="n">
         <v>9</v>
@@ -4251,10 +4318,10 @@
         <v>12</v>
       </c>
       <c r="AV21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -4301,43 +4368,43 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G22" t="n">
-        <v>0.28</v>
+        <v>0.284</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J22" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="M22" t="n">
         <v>11.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O22" t="n">
         <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q22" t="n">
         <v>0.786</v>
@@ -4346,55 +4413,55 @@
         <v>12.3</v>
       </c>
       <c r="S22" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T22" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="U22" t="n">
         <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W22" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y22" t="n">
         <v>4.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA22" t="n">
         <v>20.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>96.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.1</v>
+        <v>-5.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF22" t="n">
         <v>25</v>
       </c>
       <c r="AG22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
@@ -4412,7 +4479,7 @@
         <v>27</v>
       </c>
       <c r="AO22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP22" t="n">
         <v>9</v>
@@ -4424,19 +4491,19 @@
         <v>4</v>
       </c>
       <c r="AS22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4451,10 +4518,10 @@
         <v>19</v>
       </c>
       <c r="BB22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F23" t="n">
         <v>19</v>
       </c>
       <c r="G23" t="n">
-        <v>0.747</v>
+        <v>0.743</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J23" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
         <v>10.2</v>
@@ -4513,55 +4580,55 @@
         <v>26.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.388</v>
+        <v>0.386</v>
       </c>
       <c r="O23" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P23" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="R23" t="n">
         <v>9.9</v>
       </c>
       <c r="S23" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="T23" t="n">
         <v>43.2</v>
       </c>
       <c r="U23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V23" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W23" t="n">
         <v>7.1</v>
       </c>
       <c r="X23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y23" t="n">
         <v>3.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.2</v>
+        <v>102.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,10 +4640,10 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI23" t="n">
         <v>26</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>25</v>
       </c>
       <c r="AJ23" t="n">
         <v>26</v>
@@ -4603,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
@@ -4615,28 +4682,28 @@
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW23" t="n">
         <v>21</v>
       </c>
       <c r="AX23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY23" t="n">
         <v>2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB23" t="n">
         <v>8</v>
       </c>
       <c r="BC23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>0.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF24" t="n">
         <v>14</v>
@@ -4758,7 +4825,7 @@
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
         <v>17</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP24" t="n">
         <v>6</v>
@@ -4791,16 +4858,16 @@
         <v>26</v>
       </c>
       <c r="AT24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV24" t="n">
         <v>16</v>
       </c>
-      <c r="AU24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>15</v>
-      </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX24" t="n">
         <v>12</v>
@@ -4809,7 +4876,7 @@
         <v>14</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -4847,55 +4914,55 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F25" t="n">
         <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>0.553</v>
+        <v>0.547</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="J25" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="K25" t="n">
         <v>0.505</v>
       </c>
       <c r="L25" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.385</v>
+        <v>0.382</v>
       </c>
       <c r="O25" t="n">
         <v>20.1</v>
       </c>
       <c r="P25" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.747</v>
+        <v>0.748</v>
       </c>
       <c r="R25" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S25" t="n">
         <v>31</v>
       </c>
       <c r="T25" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U25" t="n">
         <v>23.2</v>
@@ -4910,7 +4977,7 @@
         <v>5.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z25" t="n">
         <v>20.8</v>
@@ -4919,13 +4986,13 @@
         <v>22.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>109.4</v>
+        <v>109.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4937,7 +5004,7 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>1</v>
@@ -4949,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM25" t="n">
         <v>19</v>
@@ -4967,7 +5034,7 @@
         <v>26</v>
       </c>
       <c r="AR25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS25" t="n">
         <v>10</v>
@@ -4982,7 +5049,7 @@
         <v>27</v>
       </c>
       <c r="AW25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX25" t="n">
         <v>11</v>
@@ -4994,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -5032,58 +5099,58 @@
         <v>74</v>
       </c>
       <c r="E26" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.649</v>
+        <v>0.635</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N26" t="n">
         <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R26" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T26" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="U26" t="n">
         <v>20.4</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
         <v>6.7</v>
@@ -5098,31 +5165,31 @@
         <v>20.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF26" t="n">
         <v>7</v>
       </c>
-      <c r="AF26" t="n">
-        <v>5</v>
-      </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH26" t="n">
         <v>11</v>
       </c>
       <c r="AI26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
         <v>22</v>
@@ -5140,13 +5207,13 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>17</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>18</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,16 +5222,16 @@
         <v>28</v>
       </c>
       <c r="AT26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E27" t="n">
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G27" t="n">
-        <v>0.213</v>
+        <v>0.216</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
@@ -5232,25 +5299,25 @@
         <v>81.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L27" t="n">
         <v>7.1</v>
       </c>
       <c r="M27" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.37</v>
+        <v>0.368</v>
       </c>
       <c r="O27" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="P27" t="n">
         <v>26.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.803</v>
+        <v>0.804</v>
       </c>
       <c r="R27" t="n">
         <v>10</v>
@@ -5274,22 +5341,22 @@
         <v>4.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.1</v>
+        <v>100.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.4</v>
+        <v>-8.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5304,10 +5371,10 @@
         <v>3</v>
       </c>
       <c r="AI27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK27" t="n">
         <v>23</v>
@@ -5319,7 +5386,7 @@
         <v>11</v>
       </c>
       <c r="AN27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5346,13 +5413,13 @@
         <v>26</v>
       </c>
       <c r="AW27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX27" t="n">
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ27" t="n">
         <v>29</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E28" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>0.653</v>
+        <v>0.649</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J28" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.467</v>
+        <v>0.466</v>
       </c>
       <c r="L28" t="n">
         <v>7.7</v>
@@ -5426,22 +5493,22 @@
         <v>0.388</v>
       </c>
       <c r="O28" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P28" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S28" t="n">
         <v>32.3</v>
       </c>
       <c r="T28" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U28" t="n">
         <v>21.5</v>
@@ -5456,7 +5523,7 @@
         <v>4.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
         <v>18.7</v>
@@ -5465,13 +5532,13 @@
         <v>18.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.2</v>
+        <v>96.8</v>
       </c>
       <c r="AC28" t="n">
         <v>3.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5489,10 +5556,10 @@
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>6</v>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5516,7 +5583,7 @@
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
         <v>19</v>
@@ -5543,10 +5610,10 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>-2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
         <v>22</v>
       </c>
       <c r="AF29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
         <v>22</v>
@@ -5668,13 +5735,13 @@
         <v>14</v>
       </c>
       <c r="AI29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ29" t="n">
         <v>16</v>
       </c>
       <c r="AK29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL29" t="n">
         <v>24</v>
@@ -5686,7 +5753,7 @@
         <v>9</v>
       </c>
       <c r="AO29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP29" t="n">
         <v>26</v>
@@ -5713,7 +5780,7 @@
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5725,7 +5792,7 @@
         <v>22</v>
       </c>
       <c r="BB29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -5757,22 +5824,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E30" t="n">
         <v>46</v>
       </c>
       <c r="F30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G30" t="n">
-        <v>0.605</v>
+        <v>0.613</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="J30" t="n">
         <v>80.90000000000001</v>
@@ -5787,25 +5854,25 @@
         <v>13.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O30" t="n">
         <v>21.7</v>
       </c>
       <c r="P30" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R30" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S30" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T30" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U30" t="n">
         <v>24.7</v>
@@ -5814,16 +5881,16 @@
         <v>14.9</v>
       </c>
       <c r="W30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y30" t="n">
         <v>5.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA30" t="n">
         <v>23.9</v>
@@ -5835,7 +5902,7 @@
         <v>3.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
         <v>10</v>
@@ -5847,7 +5914,7 @@
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5874,31 +5941,31 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6090,7 @@
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6056,7 +6123,7 @@
         <v>21</v>
       </c>
       <c r="AQ31" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6068,7 +6135,7 @@
         <v>23</v>
       </c>
       <c r="AU31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-3-2008-09</t>
+          <t>2009-04-03</t>
         </is>
       </c>
     </row>
